--- a/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/04_AddRedemptionTest.xlsx
+++ b/src/test/resources/testdata/Modules/06_RewardCatalogue/RewardCatalogue/04_AddRedemptionTest.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testing\Documents\Bandhan_World_APPIUM\src\test\resources\testdata\Modules\06_RewardCatalogue\RewardCatalogue\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BB5E44-D30C-4AFE-94D3-1EF8B3F4AE41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEABD0D4-2A26-4F92-B17D-13971DAA8B04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{D5674106-8292-4F40-9DFC-E6EAC771FC2F}"/>
   </bookViews>
@@ -2487,7 +2487,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
-        <v>122</v>
+        <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>126</v>
@@ -2518,7 +2518,7 @@
     </row>
     <row r="4" spans="1:15" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>123</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>126</v>
@@ -2734,7 +2734,7 @@
       </c>
     </row>
     <row r="11" spans="1:15" s="12" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
@@ -2951,7 +2951,7 @@
       </c>
     </row>
     <row r="18" spans="1:15" s="12" customFormat="1" ht="29" x14ac:dyDescent="0.35">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B18" s="1" t="s">
